--- a/templates/tpl_booking_mssnhsirnhzg.xlsx
+++ b/templates/tpl_booking_mssnhsirnhzg.xlsx
@@ -1656,7 +1656,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="123">
+  <cellXfs count="125">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1974,6 +1974,12 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2492,7 +2498,12 @@
     <row r="12" s="1" customFormat="1" ht="16.5" customHeight="1" spans="1:11">
       <c r="A12" s="50"/>
       <c r="B12" s="51"/>
-      <c r="C12" s="52"/>
+      <c r="C12" s="124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{shipper.name}}
+{{shipper.address}}</t>
+        </is>
+      </c>
       <c r="D12" s="53"/>
       <c r="E12" s="53"/>
       <c r="F12" s="53"/>
@@ -2539,13 +2550,22 @@
     <row r="15" s="1" customFormat="1" ht="16.5" customHeight="1" spans="1:11">
       <c r="A15" s="50"/>
       <c r="B15" s="51"/>
-      <c r="C15" s="52"/>
+      <c r="C15" s="124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{consignee.name}}
+{{consignee.address}}</t>
+        </is>
+      </c>
       <c r="D15" s="53"/>
       <c r="E15" s="53"/>
       <c r="F15" s="53"/>
       <c r="G15" s="53"/>
       <c r="H15" s="54"/>
-      <c r="I15" s="66"/>
+      <c r="I15" s="66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{notify.name}}</t>
+        </is>
+      </c>
       <c r="J15" s="67"/>
       <c r="K15" s="68"/>
     </row>
